--- a/client_data/client_6801/leads.xlsx
+++ b/client_data/client_6801/leads.xlsx
@@ -531,29 +531,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>restaurants in hyderabad</t>
+          <t>restaurants in Telangana</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cafe Bahar</t>
+          <t>7 Sisters Hitex</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>3-5, 815/A, Old MLA Quarters Rd, Avanti Nagar, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>6A, Hitex Road, Izzathnagar, Shilpa Hills, Hyderabad, Telangana 500084, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>040 2324 3798</t>
+          <t>075693 06793</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>50831</v>
+        <v>3502</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -572,29 +572,29 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>restaurants in hyderabad</t>
+          <t>restaurants in Telangana</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Krishnapatnam</t>
+          <t>7 Sisters</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>3rd floor, shreshta aura, Road No. 36, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
+          <t>Road No. 4, Resham Bagh, Banjara Hills, Hyderabad, Telangana 500034, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>091696 95566</t>
+          <t>093986 82574</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>28691</v>
+        <v>3428</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -613,29 +613,29 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>restaurants in hyderabad</t>
+          <t>restaurants in Telangana</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Naani’s Pure Veg</t>
+          <t>Mirosa Cafe &amp; Kitchen</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Jubilee Hills road no 1, metro pillar no C1587, Near, Jubilee Hills Check Post Rd, Park View Enclave, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
+          <t>3-6-236/2, Road, Street No 15, AP State Housing Board, Himayatnagar, Hyderabad, Telangana 500029, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>063093 09309</t>
+          <t>083411 00610</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>7182</v>
+        <v>2151</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -654,29 +654,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>restaurants in hyderabad</t>
+          <t>home cleaning services in hyderabad</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The Globe Grub | Buffet Restaurant</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SECOND FLOOR, Apurupa Towers, H.NO. 8-2-293/82/A/245, Road No. 36, behind jathara restaurant, Jawahar Colony, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
+          <t>Plot no 996 Venkatramana colony Gokul plots, KPHB, K P H B Phase 9, Hafeezpet, Hyderabad, Telangana 500085, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>083419 63277</t>
+          <t>086864 68676</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5866</v>
+        <v>863</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -695,29 +695,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>restaurants in hyderabad</t>
+          <t>home cleaning services in hyderabad</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Hummus House - Hyderabad</t>
+          <t>SS - Home Deep Cleaning &amp; Pest Control Services Hyderabad</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>H.NO.8, 2-674/B/3/2A, Road No. 12, Sri Ram Nagar Colony, Banjara Hills, Hyderabad, Telangana 500028, India</t>
+          <t>Shop No 151/152, Tulasi Building, Pragathi Nagar, Kukatpally, Hyderabad, Telangana 500090, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>080055 98005</t>
+          <t>086864 68676</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>942</v>
+        <v>855</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -736,29 +736,29 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>hair salons in Telangana</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cross Hammer Gym</t>
+          <t>PM HAIR STUDIO HAIR &amp; BEAUTY SALOON</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4th floor, Qube by Aryamitra, Rd Number 9, Huda, Alkapur Twp, Puppalguda, Manikonda, Hyderabad, Telangana 500089, India</t>
+          <t>1St Floor, Shankar Mutt, 1-8-720/1, Vegetable Market Rd, above ramreddy chicken centre, opp. Axis, Padma Colony, New Nallakunta, Hyderabad, Telangana 500044, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>063094 88555</t>
+          <t>092924 04505</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>699</v>
+        <v>827</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -782,24 +782,24 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>KING FITNESS GYM</t>
+          <t>Ultimate fitness club</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3rd floor, vasavi’shreemukh complex, 3-6-198/T/12, Himayat Nagar Rd, next to west side showroom, above union bank of India, AP State Housing Board, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>4th floor, Kakaji city centre, Khilwat road, 20-4-226, Khilwath Rd, next to Rumaan hotel, Mahboob Chowk, Khilwat, Hyderabad, Telangana 500002, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>080961 87142</t>
+          <t>078602 57865</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>536</v>
+        <v>434</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -818,29 +818,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>home cleaning services in hyderabad</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The Pet Spa</t>
+          <t>Happi Home Deep cleaning services</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3-6-253, opp. Bharat Petrol Pump, behind Suzuki bike showroom, AP State Housing Board, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>Road No. 4B, Gopal Nagar, vaishnavi avenue, Kukatpally, Hyderabad, Telangana 500085, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>093928 40349</t>
+          <t>085220 26609</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -859,29 +859,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>hair salons in Telangana</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Junnu's Pet grooming</t>
+          <t>Hair Affair Unisex Salon</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Main Rd, Adarsh Nagar Colony, Sai Homes, Peerzadiguda, Hyderabad, Telangana 500098, India</t>
+          <t>8-2-601/G/95, Road No. 10, Gouri Shankar Nagar Colony, Banjara Hills, Hyderabad, Telangana 500034, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>079899 22495</t>
+          <t>099907 77988</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -900,29 +900,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>law offices in hyderabad</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>K FITNESS CLUB</t>
+          <t>Raja Rajeshwari &amp; Co.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Pillar No.A1339, Metro Station, 5-1-521, beside V V Function Hall, Troop Bazaar, Jam Bagh, Hyderabad, Telangana 500001, India</t>
+          <t>Second Floor, SRR Nilayam, 1-2-142/13B, Street No. 6, Sai Vihar, Advocates Colony, Himayatnagar, Hyderabad, Telangana 500029, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>098851 63539</t>
+          <t>082971 38888</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -941,29 +941,29 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>auto repair shops in hyderabad</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Pets Vegas</t>
+          <t>MG CAR CARE</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>M, Ground Floor, 3-6-584, Street Number 8, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>1-2-621, a elchiguda, Lower Tank Bund, Kavadiguda, Hyderabad, Telangana 500080, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>096660 71727</t>
+          <t>081797 58156</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -982,29 +982,29 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>pet grooming in Telangana</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Women Power Fitness Club in Hyderabad</t>
+          <t>Absolute Pets - Grooming Salon</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Bushra Hospital ,2nd floor, near water tank ,Moghalpura, 23-2-260, Moghalpura, Hyderabad, Telangana 500002, India</t>
+          <t>Shop 3, MRK Rd, next to HP Gas), J S Arcade, Sri, Ram Nagar Colony, Alwal, Secunderabad, Telangana 500015, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>070755 50440</t>
+          <t>063003 55518</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
         <v>4.7</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>294</v>
+        <v>188</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1023,29 +1023,29 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>auto repair shops in hyderabad</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>FAT TO FIT GYM</t>
+          <t>Germany Motors</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1247 Gokul Plots V.R.Colony, Opp:, Prajay Megapolis, Kukatpally Housing Board Colony, Venkata Ramana Colony, Hafeezpet, Hyderabad, Telangana 500085, India</t>
+          <t>Kuntlor Haythnagar,Kuntlor to Nagole Road, 8JG2+VW9 Narayana Junior College, Kuntloor Rd, beside Nagole Road, Boggula Darshan Reddy Nagar, Hayathnagar_Khalsa, Hyderabad, Telangana 501505, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>091335 51813</t>
+          <t>095507 76871</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>231</v>
+        <v>179</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1064,29 +1064,29 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>fitness centers in hyderabad</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Super pet grooming services</t>
+          <t>PFC Unisex Gym Malakpet</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Sardarpatel nagar, x road, near community hall, Kukatpally Housing Board Colony, Dharma Reddy Colony Phase II, Nizampet, Hyderabad, Telangana 500085, India</t>
+          <t>2nd Floor, Zudio Building, opp. metro pillar no:1456, Anand Nagar Colony, New Malakpet, Hyderabad, Telangana 500036, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>098495 38601</t>
+          <t>074167 69922</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>226</v>
+        <v>166</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1105,29 +1105,29 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>hair salons in hyderabad</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sreenivasa PET SPA &amp; PARLOUR</t>
+          <t>Purple Smoke Hair Studio</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Vittalwadi Ln, Vittalwadi, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>36 Pinnacle, Jubilee hills Road no.36, Metro pillar No. C1618, Jawahar Colony, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>097053 16434</t>
+          <t>083284 64765</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1146,29 +1146,29 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>pet grooming in Telangana</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Nail to Tails Pet Grooming Parlour</t>
+          <t>Furries N Paws</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11-110 P&amp;T Colony, Pragati Nagar, Sharada Theatre Rd, Saroornagar, Sahithi Nagar, Dilsukhnagar, Hyderabad, Telangana 500060, India</t>
+          <t>2-2, 1012, Buruju Galli, Tulasi Nagar Colony, Bagh Amberpet, Amberpet, Hyderabad, Telangana 500013, India</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>070135 71954</t>
+          <t>085009 11020</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>185</v>
+        <v>84</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
@@ -1187,29 +1187,29 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>auto repair shops in hyderabad</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Beauty in the Beast pet grooming parlour</t>
+          <t>Torque Auto</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>beside Ananya copier services Xerox, opposite Food Court, Balaji Enclave, Beerappagadda, Gaddi annaram, Secunderabad, Hyderabad, Telangana 500039, India</t>
+          <t>Rd Number 11, behind ACT Fibernet, Mithila Nagar, Banjara Hills, Hyderabad, Telangana 500034, India</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>079891 69551</t>
+          <t>077026 49650</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
@@ -1228,29 +1228,29 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>pet grooming in Telangana</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>BEAST Garage The Gym</t>
+          <t>The Pet Hub Spa / Pet Store Manikonda</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17-1-177/10, near Harmain Hotel, Srinagar Colony, Madannapet Colony, Hyderabad, Telangana 500059, India</t>
+          <t>13, Alkapur Main Rd, Alkapur Twp, Puppalguda, Manikonda, Hyderabad, Telangana 500089, India</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>099894 91949</t>
+          <t>088850 33203</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
@@ -1269,29 +1269,29 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in hyderabad</t>
+          <t>real estate agencies in hyderabad</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Fatima pet Grooming</t>
+          <t>Bandari Real Estates in Hyderabad</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Wahed Nagar, Old Malakpet, Hyderabad, Telangana 500036, India</t>
+          <t>Raghavendra Apartments,Flat no:50O5, near Minerva Hotel, RBI Colony, Himayatnagar, Hyderabad, Telangana 500020, India</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>093471 60794</t>
+          <t>099597 78353</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -1310,29 +1310,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>restaurants in hyderabad</t>
+          <t>auto repair shops in hyderabad</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Illu The Restaurant</t>
+          <t>Meherun Motors 24 Hours Car Garage</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>775D, Masthan Nagar, CBI Colony, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
+          <t>1-2-607/32/2 Ambedkar nagar, NTR Stadium Rd, opp. LIC Office, BM Nagar, Gandhi Nagar, Kavadiguda, Hyderabad, Telangana 500080, India</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>090324 35511</t>
+          <t>091008 06591</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>4836</v>
+        <v>157</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/illu_hyderabad?igsh=Z3VwdWZocTQ5Mm1y</t>
+          <t>https://instagram.com/meherun_motors?igshid=YmMyMTA2M2Y=</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>

--- a/client_data/client_6801/leads.xlsx
+++ b/client_data/client_6801/leads.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Leads" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$L$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -469,6 +469,7 @@
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -519,10 +520,15 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>E-commerce Platform</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Weak Points</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>PageSpeed Score (mobile)</t>
         </is>
@@ -536,24 +542,24 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>7 Sisters Hitex</t>
+          <t>Fursat kitchen &amp; Bar</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>6A, Hitex Road, Izzathnagar, Shilpa Hills, Hyderabad, Telangana 500084, India</t>
+          <t>Capital Pk Rd, Ayyappa Society, VIP Hills, Silicon Valley, Madhapur, Hyderabad, Telangana 500081, India</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>075693 06793</t>
+          <t>090596 70033</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3502</v>
+        <v>2962</v>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
@@ -568,33 +574,34 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Telangana</t>
+          <t>restaurants in India</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7 Sisters</t>
+          <t>1135 AD</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Road No. 4, Resham Bagh, Banjara Hills, Hyderabad, Telangana 500034, India</t>
+          <t>1135 AD, Amber Palace, Jaleb Chowk, Devisinghpura, Amer, Jaipur, Jaipur Heritage (M Corp.) (Part), Rajasthan 302028, India</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>093986 82574</t>
+          <t>098290 37170</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>4.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3428</v>
+        <v>1872</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -609,33 +616,34 @@
       <c r="I3" s="2" t="inlineStr"/>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>restaurants in Telangana</t>
+          <t>hair salons in India</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mirosa Cafe &amp; Kitchen</t>
+          <t>LUJO SALON</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>3-6-236/2, Road, Street No 15, AP State Housing Board, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>Isiri Stone Creek Block-2, Yelenahalli Main Rd, Akshayanagara West, DLF Newtown, Akshayanagar, Bengaluru, Karnataka 560114, India</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>083411 00610</t>
+          <t>099166 38989</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2151</v>
+        <v>1196</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -650,33 +658,34 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>home cleaning services in hyderabad</t>
+          <t>home cleaning services in Telangana</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>ICON HOME CLEANING SERVICES</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Plot no 996 Venkatramana colony Gokul plots, KPHB, K P H B Phase 9, Hafeezpet, Hyderabad, Telangana 500085, India</t>
+          <t>HNO 1-87, near Mena cafe, Masjid Banda, NCB Enclave, Gachibowli, Hyderabad, Telangana 500084, India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>086864 68676</t>
+          <t>099858 35690</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>863</v>
+        <v>543</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
@@ -691,33 +700,34 @@
       <c r="I5" s="2" t="inlineStr"/>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>home cleaning services in hyderabad</t>
+          <t>fitness centers in Telangana</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SS - Home Deep Cleaning &amp; Pest Control Services Hyderabad</t>
+          <t>MAXX FITNESS UNISEX GYM</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Shop No 151/152, Tulasi Building, Pragathi Nagar, Kukatpally, Hyderabad, Telangana 500090, India</t>
+          <t>1-7-19, Opp Nird Arch, Ambedkar Nagar Colony, Telangana state, Rajendranagar mandal, Hyderabad, Telangana 500030, India</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>086864 68676</t>
+          <t>097009 51746</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>855</v>
+        <v>474</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
@@ -732,33 +742,34 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>hair salons in Telangana</t>
+          <t>restaurants in Telangana</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PM HAIR STUDIO HAIR &amp; BEAUTY SALOON</t>
+          <t>Gol Banglow Unique Dining - Taj Falaknuma</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1St Floor, Shankar Mutt, 1-8-720/1, Vegetable Market Rd, above ramreddy chicken centre, opp. Axis, Padma Colony, New Nallakunta, Hyderabad, Telangana 500044, India</t>
+          <t>TAJ FALAKNUMA PALACE, Engine Bowli, Falaknuma, Fatima Nagar, Falaknuma, Hyderabad, Telangana 500053, India</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>092924 04505</t>
+          <t>040 6629 8585</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>827</v>
+        <v>360</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -773,33 +784,34 @@
       <c r="I7" s="2" t="inlineStr"/>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>fitness centers in Telangana</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ultimate fitness club</t>
+          <t>Fitness First Gym</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4th floor, Kakaji city centre, Khilwat road, 20-4-226, Khilwath Rd, next to Rumaan hotel, Mahboob Chowk, Khilwat, Hyderabad, Telangana 500002, India</t>
+          <t>beside La-Delicious Bakery, near Court Chowrasta, Jyothinagar, Karimnagar, Telangana 505001, India</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>078602 57865</t>
+          <t>097004 09010</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>434</v>
+        <v>350</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
@@ -814,33 +826,34 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>home cleaning services in hyderabad</t>
+          <t>fitness centers in Telangana</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Happi Home Deep cleaning services</t>
+          <t>THE FIT NATION HYDERABAD | KOTHAPET</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Road No. 4B, Gopal Nagar, vaishnavi avenue, Kukatpally, Hyderabad, Telangana 500085, India</t>
+          <t>Kothapet Rd, Laxmi Nagar Colony, Kothapet, Hyderabad, Telangana 500102, India</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>085220 26609</t>
+          <t>079897 76527</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>377</v>
+        <v>226</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
@@ -855,33 +868,34 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>hair salons in Telangana</t>
+          <t>auto repair shops in Telangana</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Hair Affair Unisex Salon</t>
+          <t>Diablo Automotive</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8-2-601/G/95, Road No. 10, Gouri Shankar Nagar Colony, Banjara Hills, Hyderabad, Telangana 500034, India</t>
+          <t>Homes Road 7, 52/5/23/A/1, Muppas Rd, behind MY HOME AVATAR, Indiramma colony, Narsingi, Hyderabad, Telangana 500075, India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>099907 77988</t>
+          <t>080198 27888</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>366</v>
+        <v>201</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -896,33 +910,34 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>law offices in hyderabad</t>
+          <t>pet grooming in India</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Raja Rajeshwari &amp; Co.</t>
+          <t>Petsburgh Grooming Salon &amp; Academy</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Second Floor, SRR Nilayam, 1-2-142/13B, Street No. 6, Sai Vihar, Advocates Colony, Himayatnagar, Hyderabad, Telangana 500029, India</t>
+          <t>Rushabh Complex, 07-08, Veera Desai Rd, opposite Fun Republic Road, Veera Desai Industrial Estate, Andheri West, Mumbai, Maharashtra 400053, India</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>082971 38888</t>
+          <t>074001 93970</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>330</v>
+        <v>192</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
@@ -937,33 +952,34 @@
       <c r="I11" s="2" t="inlineStr"/>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>auto repair shops in hyderabad</t>
+          <t>pet grooming in India</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MG CAR CARE</t>
+          <t>Pampurr Pets Grooming Salon and Spa</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1-2-621, a elchiguda, Lower Tank Bund, Kavadiguda, Hyderabad, Telangana 500080, India</t>
+          <t>Shop No, Ground floor, Crystal Colony, A-2, MMC Cross Rd Number 2, near Canossa High School, Mahim (W), Central Government Staff Colony, Mahim, Mumbai, Maharashtra 400016, India</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>081797 58156</t>
+          <t>098193 99281</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
         <v>4.9</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
@@ -978,33 +994,34 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in Telangana</t>
+          <t>home cleaning services in Telangana</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Absolute Pets - Grooming Salon</t>
+          <t>HMD deep cleaning services</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Shop 3, MRK Rd, next to HP Gas), J S Arcade, Sri, Ram Nagar Colony, Alwal, Secunderabad, Telangana 500015, India</t>
+          <t>Maruthi Nagar, Hyderabad, Badangpet, Telangana 500112, India</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>063003 55518</t>
+          <t>063055 52831</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
@@ -1019,33 +1036,34 @@
       <c r="I13" s="2" t="inlineStr"/>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>auto repair shops in hyderabad</t>
+          <t>auto repair shops in Telangana</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Germany Motors</t>
+          <t>JM Automotives</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Kuntlor Haythnagar,Kuntlor to Nagole Road, 8JG2+VW9 Narayana Junior College, Kuntloor Rd, beside Nagole Road, Boggula Darshan Reddy Nagar, Hayathnagar_Khalsa, Hyderabad, Telangana 501505, India</t>
+          <t>NH65, near Value Zone Hypermart, opposite Novpan Industries, Patancheru Industrial Area, Patancheruvu, Telangana 502319, India</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>095507 76871</t>
+          <t>096764 83526</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
         <v>4.8</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
@@ -1060,33 +1078,34 @@
       <c r="I14" s="2" t="inlineStr"/>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>fitness centers in hyderabad</t>
+          <t>auto repair shops in Telangana</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>PFC Unisex Gym Malakpet</t>
+          <t>Mokshitha Sri Motors And Car Care</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2nd Floor, Zudio Building, opp. metro pillar no:1456, Anand Nagar Colony, New Malakpet, Hyderabad, Telangana 500036, India</t>
+          <t>5-45, Road No. 1, opp. Savitha Petrol Bunk, Mytri Vanam, Siddipet, Telangana 502103, India</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>074167 69922</t>
+          <t>099855 96434</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>166</v>
+        <v>49</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
@@ -1101,33 +1120,34 @@
       <c r="I15" s="2" t="inlineStr"/>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>hair salons in hyderabad</t>
+          <t>pet grooming in India</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Purple Smoke Hair Studio</t>
+          <t>Dog grooming service ( Providing Home Service Only )</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>36 Pinnacle, Jubilee hills Road no.36, Metro pillar No. C1618, Jawahar Colony, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
+          <t>Cluster_mumbai Suburban_689 Horizon, RTO Ln, Shatataraka Co Op Housing Society, serenity Lane, Andheri West, Mumbai, Maharashtra 400053, India</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>083284 64765</t>
+          <t>075587 24312</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
@@ -1142,197 +1162,214 @@
       <c r="I16" s="2" t="inlineStr"/>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in Telangana</t>
+          <t>restaurants in Telangana</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Furries N Paws</t>
+          <t>Telugu Medium Kitchen &amp; Bar</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2-2, 1012, Buruju Galli, Tulasi Nagar Colony, Bagh Amberpet, Amberpet, Hyderabad, Telangana 500013, India</t>
+          <t>Plot No.1062, Road No 46, Nandagiri Hills, Jubilee Hills, Hyderabad, Telangana 500033, India</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>085009 11020</t>
+          <t>092811 22083</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>3166</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/telugumediumkitchen/</t>
+        </is>
+      </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>auto repair shops in hyderabad</t>
+          <t>hair salons in India</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Torque Auto</t>
+          <t>THE INDIAN SALON</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Rd Number 11, behind ACT Fibernet, Mithila Nagar, Banjara Hills, Hyderabad, Telangana 500034, India</t>
+          <t>GF-5,6, PALASH PEARL, MG Rd, nr. MALABAR HILLS, New India Colony, Nikol, Ahmedabad, Gujarat 380049, India</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>077026 49650</t>
+          <t>075758 69696</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>1206</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_indian_salon_/?hl=en</t>
+        </is>
+      </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>pet grooming in Telangana</t>
+          <t>pet grooming in India</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The Pet Hub Spa / Pet Store Manikonda</t>
+          <t>Pet Society - Pet grooming spa | Pet store</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13, Alkapur Main Rd, Alkapur Twp, Puppalguda, Manikonda, Hyderabad, Telangana 500089, India</t>
+          <t>4th Main Rd, SBI Staff Colony, Hoshalli Extension, Stage 1, Vijayanagar, Bengaluru, Karnataka 560040, India</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>088850 33203</t>
+          <t>096064 54400</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>244</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/petsocietyblr?igsh=bXRoejZsNm1ld3I2</t>
+        </is>
+      </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>real estate agencies in hyderabad</t>
+          <t>fitness centers in Telangana</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Bandari Real Estates in Hyderabad</t>
+          <t>Fitness 365 Gym- Nagaram Hyderabad</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Raghavendra Apartments,Flat no:50O5, near Minerva Hotel, RBI Colony, Himayatnagar, Hyderabad, Telangana 500020, India</t>
+          <t>3rd Floor, Dattari Towers, 3-43/1, Hanuman Temple Rd, above Croma, Aravind Nagar, Nagaram, Keesara, Secunderabad, Telangana 500083, India</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>099597 78353</t>
+          <t>095042 81281</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>No website</t>
+        <v>241</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Social media only</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Strong reviews, no way to showcase/book online</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>Good social presence, missing a proper website</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fitness365_nagaram/?igsh=MTNoYXMzaW1sa2w2Mg%3D%3D</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>auto repair shops in hyderabad</t>
+          <t>auto repair shops in Telangana</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Meherun Motors 24 Hours Car Garage</t>
+          <t>Dynamic Car Work Shop</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1-2-607/32/2 Ambedkar nagar, NTR Stadium Rd, opp. LIC Office, BM Nagar, Gandhi Nagar, Kavadiguda, Hyderabad, Telangana 500080, India</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>091008 06591</t>
-        </is>
-      </c>
+          <t>Langar Houz, Hyderabad, Telangana 500008, India</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
       <c r="E21" s="2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1346,14 +1383,15 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>https://instagram.com/meherun_motors?igshid=YmMyMTA2M2Y=</t>
+          <t>https://www.instagram.com/dynamiccarworkshop?igsh=MXMzOWJ1bmo3MjJucg==</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:L21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>